--- a/data/Oficina_de_procuradora_de_mujeres/opmTasas.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmTasas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kryshiha/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90D9D012-6578-5040-B3B9-71B64982CE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AD5157-0714-483D-9A2D-6BE5062C5E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="17080" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,8 +61,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -112,10 +112,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
@@ -133,13 +133,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -178,7 +181,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="35" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -198,7 +201,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -218,7 +221,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -315,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0AC9E31-C370-4ADE-8057-A490A009DA21}" name="Table1" displayName="Table1" ref="A1:G36" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G36" xr:uid="{D0AC9E31-C370-4ADE-8057-A490A009DA21}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D0AC9E31-C370-4ADE-8057-A490A009DA21}" name="Table1" displayName="Table1" ref="A1:G37" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G37" xr:uid="{D0AC9E31-C370-4ADE-8057-A490A009DA21}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{4E633C29-01F9-4BB3-B2C3-5A220C104F5B}" name="Año" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{B3049418-5001-4BD0-8583-9B4F513F7599}" name="Asesinatos" dataDxfId="5"/>
@@ -651,19 +654,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -686,7 +689,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1990</v>
       </c>
@@ -711,7 +714,7 @@
         <v>1.4410464077138307E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1991</v>
       </c>
@@ -728,7 +731,7 @@
         <v>3550566</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F36" si="1">B3/D3*100000</f>
+        <f t="shared" ref="F3:F37" si="1">B3/D3*100000</f>
         <v>1.7465437536500035</v>
       </c>
       <c r="G3" s="8">
@@ -736,7 +739,7 @@
         <v>3.6543753650003508E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1992</v>
       </c>
@@ -761,7 +764,7 @@
         <v>1.2754392124735059E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>1993</v>
       </c>
@@ -786,7 +789,7 @@
         <v>2.5641045495632842E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1994</v>
       </c>
@@ -811,7 +814,7 @@
         <v>2.0344839543450455E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>1995</v>
       </c>
@@ -836,7 +839,7 @@
         <v>2.0150893882237009E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>1996</v>
       </c>
@@ -861,7 +864,7 @@
         <v>1.3448444439548624E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>1997</v>
       </c>
@@ -886,7 +889,7 @@
         <v>1.3627701788377689E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>1998</v>
       </c>
@@ -911,7 +914,7 @@
         <v>3.6550563313977324E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>1999</v>
       </c>
@@ -936,7 +939,7 @@
         <v>7.2903190263475803E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>2000</v>
       </c>
@@ -961,7 +964,7 @@
         <v>-5.0540309021240848E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2001</v>
       </c>
@@ -986,7 +989,7 @@
         <v>-1.7036208730545344E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2002</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>-4.4128105274452434E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>2003</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>-2.3701948913235071E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>2004</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>-1.1096483243941968E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>2005</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>-2.9409597290708245E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>2006</v>
       </c>
@@ -1111,7 +1114,7 @@
         <v>2.0528117636122722E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>2007</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>1.9214032357278699E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>2008</v>
       </c>
@@ -1161,7 +1164,7 @@
         <v>-1.7921865621128852E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>2009</v>
       </c>
@@ -1186,7 +1189,7 @@
         <v>1.624752678111685E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>2010</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>3.6971842064678073E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>2011</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>-4.7153200218661429E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>2012</v>
       </c>
@@ -1261,7 +1264,7 @@
         <v>-3.4040020765879753E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>2013</v>
       </c>
@@ -1286,7 +1289,7 @@
         <v>-2.2668073475128336E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>2014</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>-3.2554707831253804E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>2015</v>
       </c>
@@ -1336,7 +1339,7 @@
         <v>-4.642872278769361E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>2016</v>
       </c>
@@ -1361,7 +1364,7 @@
         <v>-2.1734700846280375E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>2017</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>5.5172129155334204E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>2018</v>
       </c>
@@ -1411,7 +1414,7 @@
         <v>2.0350620577422873E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>2019</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>-4.0428540864483331E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>2020</v>
       </c>
@@ -1453,7 +1456,7 @@
         <v>3281557</v>
       </c>
       <c r="F32" s="7">
-        <f t="shared" si="1"/>
+        <f>B32/D32*100000</f>
         <v>0.63713008806296234</v>
       </c>
       <c r="G32" s="8">
@@ -1461,98 +1464,121 @@
         <v>-2.8699119370376724E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>2021</v>
       </c>
       <c r="B33" s="5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C33" s="5">
         <v>0.69</v>
       </c>
       <c r="D33" s="6">
-        <v>1718448</v>
+        <v>1722149</v>
       </c>
       <c r="E33" s="6">
-        <v>3262693</v>
+        <v>3262731</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" si="1"/>
-        <v>1.0474567749504204</v>
+        <f>B33/D33*100000</f>
+        <v>1.2194066831615615</v>
       </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
-        <v>0.3574567749504205</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>0.52940668316156159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>2022</v>
       </c>
       <c r="B34" s="5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="6">
-        <v>1698378</v>
+        <v>1702078</v>
       </c>
       <c r="E34" s="6">
-        <v>3220113</v>
+        <v>3220148</v>
       </c>
       <c r="F34" s="7">
-        <f t="shared" si="1"/>
-        <v>0.76543619853766354</v>
+        <f>B34/D34*100000</f>
+        <v>0.99877913938139151</v>
       </c>
       <c r="G34" s="8">
         <f t="shared" si="0"/>
-        <v>0.76543619853766354</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>0.99877913938139151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>2023</v>
       </c>
       <c r="B35" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="6">
-        <v>1691987</v>
+        <v>1694807</v>
       </c>
       <c r="E35" s="6">
-        <v>3205691</v>
+        <v>3203794</v>
       </c>
       <c r="F35" s="7">
         <f>B35/D35*100000</f>
-        <v>1.2411442877516199</v>
+        <v>1.7111092885502597</v>
       </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
-        <v>1.2411442877516199</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>1.7111092885502597</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>2024</v>
       </c>
       <c r="B36" s="5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="1">
-        <v>1691136</v>
+        <v>1694107</v>
       </c>
       <c r="E36" s="3">
-        <v>3203295</v>
+        <v>3202521</v>
       </c>
       <c r="F36" s="7">
-        <f t="shared" si="1"/>
-        <v>1.2417688465031789</v>
+        <f>B36/D36*100000</f>
+        <v>1.6527881650922875</v>
       </c>
       <c r="G36" s="8">
         <f t="shared" si="0"/>
-        <v>1.2417688465031789</v>
+        <v>1.6527881650922875</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B37" s="5">
+        <v>21</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="9">
+        <v>1686080</v>
+      </c>
+      <c r="E37" s="9">
+        <v>3184835</v>
+      </c>
+      <c r="F37" s="7">
+        <f>B37/D37*100000</f>
+        <v>1.2454925033213133</v>
+      </c>
+      <c r="G37" s="8">
+        <f>F37-C37</f>
+        <v>1.2454925033213133</v>
       </c>
     </row>
   </sheetData>
